--- a/Web/TestCases/Suscripcion.xlsx
+++ b/Web/TestCases/Suscripcion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BDC345-9B4D-4BFA-B7F8-FC7500ED8BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA2312F-C849-46AE-85DB-5C740D28902A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="1110" windowWidth="28710" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Num</t>
   </si>
@@ -70,9 +70,6 @@
     <t>KO</t>
   </si>
   <si>
-    <t>La ruta a la página por igualar al resto debería ser Inicio/subscription, hay q revisar todo el tema de tildes, y cuidar las palabras en inglés "Free" y poner su correspondencia en castellano.</t>
-  </si>
-  <si>
     <t>1. The subscription plan is activated</t>
   </si>
   <si>
@@ -95,6 +92,16 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1dNTkvOk1XKmTDi5pC_ohKwqyVAKlTP9n/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>La ruta a la página por igualar al resto debería ser Inicio/subscription, hay q revisar todo el tema de tildes, y cuidar las palabras en inglés "Free" y poner su correspondencia en castellano(Gratuito)</t>
+  </si>
+  <si>
+    <t>1.The user clicks "Suscripción"</t>
+  </si>
+  <si>
+    <t>1.The user clicks "Suscripción"
+2. Clicks "Subscribirse ahora"</t>
   </si>
 </sst>
 </file>
@@ -571,7 +578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -581,18 +588,20 @@
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -603,23 +612,25 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -627,15 +638,17 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" s="4"/>
     </row>
